--- a/decomposition.xlsx
+++ b/decomposition.xlsx
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -788,11 +788,11 @@
         </is>
       </c>
       <c r="B3" s="10" t="n">
-        <v>80000</v>
+        <v>87500</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>← ПОД ВОПРОСОМ — уточнить</t>
+          <t>середина 75-100к</t>
         </is>
       </c>
     </row>
@@ -1035,8 +1035,16 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>• Срок 1 заказа делегирования: 2–3 недели → рост числа заказов = только через делегатов (параллельные потоки), не своим временем.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A13:H13"/>

--- a/decomposition.xlsx
+++ b/decomposition.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Расходы" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Доходы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Сводка" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -105,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,6 +122,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -728,7 +730,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>⚠ Жильё = 0: подтвердить, что нет аренды/ипотеки. Долги 22 200 = 266 400 ₽ ÷ 12 мес.</t>
+          <t>Допущение: жильё = 0 (нет аренды/ипотеки). Долги 22 200 = 266 400 ₽ ÷ 12 мес.</t>
         </is>
       </c>
     </row>
@@ -752,7 +754,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -775,11 +777,6 @@
       <c r="B2" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>← правь под актуальный</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -824,7 +821,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Цена/ед., ₽</t>
+          <t>Доход с ед., ₽</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -909,7 +906,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="n">
-        <v>408000</v>
+        <v>157500</v>
       </c>
       <c r="H8" s="12">
         <f>IF(D8=0,"—",ROUND(G8/D8,1))</f>
@@ -954,7 +951,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Академия / проекты RealMind (потенциал)</t>
+          <t>Академия / проекты RealMind</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -963,7 +960,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -973,7 +970,7 @@
         <v/>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>250500</v>
       </c>
       <c r="H10" s="12">
         <f>IF(D10=0,"—",ROUND(G10/D10,1))</f>
@@ -1003,42 +1000,42 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Пояснения:</t>
+          <t>Пояснения к плану (цель 750 000 ₽/мес):</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>• Гипнотерапия: $150/сессия × курс. Сейчас 4/мес, цель 16/мес (программа — цена может быть выше).</t>
+          <t>• Гипнотерапия: $150/сессия × курс 80. Рост 4 → 16 сессий/мес (программа, цена может быть выше).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>• Делегирование: доход = 30% × средний чек. Сейчас ~3-4 заказа/мес (часть отменяется).</t>
+          <t>• Делегирование: 30% × 87 500 = 26 250 ₽/заказ. 1 заказ = 2–3 недели → рост числа заказов только через делегатов (параллельные потоки). В плане 6 заказов/мес по текущей мощности.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>• Почасовая: 2500 ₽/ч × ~10 ч/нед (≈43,3 ч/мес).</t>
+          <t>• Почасовая: 2 500 ₽/ч, рост до 60 ч/мес (~14 ч/нед).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>• «Нужно ед./мес» — сколько надо продать/отработать для плановой суммы.</t>
+          <t>• RealMind/Академия: цена проекта 50 000 ₽ — ЗАГЛУШКА, задать реальную. Этот канал закрывает разрыв цели (~250 500).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>• Срок 1 заказа делегирования: 2–3 недели → рост числа заказов = только через делегатов (параллельные потоки), не своим временем.</t>
+          <t>• «Нужно ед./мес» — сколько продать/отработать, чтобы выйти на плановую сумму.</t>
         </is>
       </c>
     </row>
@@ -1054,4 +1051,87 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>СВОДКА</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Расходы, факт / мес</t>
+        </is>
+      </c>
+      <c r="B3" s="13">
+        <f>Расходы.C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Доход, факт / мес</t>
+        </is>
+      </c>
+      <c r="B4" s="13">
+        <f>Доходы.F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Профицит сейчас (доход − расход)</t>
+        </is>
+      </c>
+      <c r="B5" s="13">
+        <f>B4-B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Цель дохода / мес</t>
+        </is>
+      </c>
+      <c r="B6" s="13">
+        <f>Доходы.B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>До цели (цель − факт дохода)</t>
+        </is>
+      </c>
+      <c r="B7" s="13">
+        <f>B6-B4</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/decomposition.xlsx
+++ b/decomposition.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Расходы" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Доходы" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Сводка" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Декомпозиция" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Доп. расчёты" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="# ##0 ₽"/>
+    <numFmt numFmtId="164" formatCode="# ##0 &quot;₽&quot;"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -37,29 +36,27 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <color rgb="00222222"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00111111"/>
-      <sz val="11"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00B26A00"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00D1B16A"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="000057B8"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00D1B16A"/>
+      <i val="1"/>
+      <color rgb="008A6D3B"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -90,39 +87,47 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="003A3F4B"/>
+        <color rgb="009AA0AA"/>
       </left>
       <right style="thin">
-        <color rgb="003A3F4B"/>
+        <color rgb="009AA0AA"/>
       </right>
       <top style="thin">
-        <color rgb="003A3F4B"/>
+        <color rgb="009AA0AA"/>
       </top>
       <bottom style="thin">
-        <color rgb="003A3F4B"/>
+        <color rgb="009AA0AA"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,255 +493,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ДЕКОМПОЗИЦИЯ — Расходы (ежемесячно, ₽)</t>
+          <t>декомпозиция</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>статья расхода</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>сумма, ₽/мес</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>источники дохода</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>стоимость ежемесячно</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>штук в месяц</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Категория</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Сумма/мес, ₽</t>
-        </is>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>жильё (аренда, ипотека, платежи)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Гипнотерапия</t>
+        </is>
+      </c>
+      <c r="F3" s="4">
+        <f>'Доп. расчёты'!$B$2*150</f>
+        <v/>
+      </c>
+      <c r="G3" s="5">
+        <f>ROUND('Доп. расчёты'!$B$4/F3,1)</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Жильё (аренда, ипотека, платежи)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>долги, кредиты, рассрочки</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>22200</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Автоматизация — делегирование процессов (30%)</t>
+        </is>
+      </c>
+      <c r="F4" s="4">
+        <f>0.3*'Доп. расчёты'!$B$3</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>ROUND('Доп. расчёты'!$B$4/F4,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>инвестиции в себя (обучение, спорт, творчество)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Автоматизация — почасовая (2 клиента)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G5" s="5">
+        <f>ROUND('Доп. расчёты'!$B$4/F5,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>здоровье (бады, обследования, массажи, процедуры)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Академия / проекты RealMind</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G6" s="5">
+        <f>ROUND('Доп. расчёты'!$B$4/F6,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>транспорт (аренда, замена расходников, топливо)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>итого (цель дохода):</t>
+        </is>
+      </c>
+      <c r="F7" s="8">
+        <f>'Доп. расчёты'!$B$4</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>одежда, аксессуары, косметика, уход за собой</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>гаджеты (телефоны, камеры, связь, интернет)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Долги, кредиты, рассрочки (266 400 ÷ 12)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>22200</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Инвестиции в себя (обучение, спорт, творчество)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Здоровье (бады, обследования, массаж)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Транспорт (топливо, расходники)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Одежда, косметика, уход</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1500</v>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Гаджеты, связь, интернет</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>бизнес (только личный бренд)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Бизнес (личный бренд)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>питание (продукты, кафе, рестораны, доставка)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>подарки (себе, родным, друзьям) — ДР, праздники</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>отдых (выходные, отпуск)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Питание (продукты, кафе, доставка)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Подарки (ДР, праздники)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>5000</v>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Отдых (выходные, отпуск)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>путешествия</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Путешествия</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>0</v>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>подписки услуг (приложения, музыка, кино)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Подписки (приложения, музыка, кино)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>500</v>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>визы (визараны)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Визы (визараны)</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>благотворительность</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Благотворительность</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>ИТОГО расходов</t>
-        </is>
-      </c>
-      <c r="C19" s="7">
-        <f>SUM(C4:C18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Допущение: жильё = 0 (нет аренды/ипотеки). Долги 22 200 = 266 400 ₽ ÷ 12 мес.</t>
-        </is>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>итого:</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>SUM(B3:B17)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -748,53 +792,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ДЕКОМПОЗИЦИЯ — Источники дохода (₽/мес)</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ПАРАМЕТРЫ И РАСЧЁТЫ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Курс $ (₽)</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Средний чек заказа (делегирование), ₽</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>87500</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>середина 75-100к</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Цель дохода / мес, ₽</t>
         </is>
@@ -804,333 +838,164 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Источник дохода</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Доход с ед., ₽</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Ед./мес
-(факт)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Доход факт/мес</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>План доход/мес</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Нужно ед./мес
-(план)</t>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>ФАКТ (сейчас)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>источник</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>ед./мес (факт)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>доход факт/мес</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Гипнотерапия</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>сессия</t>
-        </is>
-      </c>
-      <c r="D7" s="4">
-        <f>150*$B$2</f>
-        <v/>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="B8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="4">
-        <f>D7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>192000</v>
-      </c>
-      <c r="H7" s="12">
-        <f>IF(D7=0,"—",ROUND(G7/D7,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Автоматизация — делегирование (30% от заказа)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>заказ</t>
-        </is>
-      </c>
-      <c r="D8" s="4">
-        <f>0.3*$B$3</f>
-        <v/>
-      </c>
-      <c r="E8" s="3" t="n">
+      <c r="C8" s="14">
+        <f>B8*'Декомпозиция'!F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Автоматизация — делегирование (30%)</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
         <v>3.5</v>
       </c>
-      <c r="F8" s="4">
-        <f>D8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>157500</v>
-      </c>
-      <c r="H8" s="12">
-        <f>IF(D8=0,"—",ROUND(G8/D8,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="14">
+        <f>B9*'Декомпозиция'!F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Автоматизация — почасовая (2 клиента)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>час</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E9" s="3" t="n">
+      <c r="B10" s="13" t="n">
         <v>43.3</v>
       </c>
-      <c r="F9" s="4">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H9" s="12">
-        <f>IF(D9=0,"—",ROUND(G9/D9,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="C10" s="14">
+        <f>B10*'Декомпозиция'!F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Академия / проекты RealMind</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>проект</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E10" s="3" t="n">
+      <c r="B11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="4">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>250500</v>
-      </c>
-      <c r="H10" s="12">
-        <f>IF(D10=0,"—",ROUND(G10/D10,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="7">
-        <f>SUM(F7:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="7">
-        <f>SUM(G7:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Пояснения к плану (цель 750 000 ₽/мес):</t>
-        </is>
+      <c r="C11" s="14">
+        <f>B11*'Декомпозиция'!F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГО факт</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="17">
+        <f>SUM(C8:C11)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>• Гипнотерапия: $150/сессия × курс 80. Рост 4 → 16 сессий/мес (программа, цена может быть выше).</t>
-        </is>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Профицит сейчас (доход факт − расходы)</t>
+        </is>
+      </c>
+      <c r="B14" s="18">
+        <f>C12-Декомпозиция!B18</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>• Делегирование: 30% × 87 500 = 26 250 ₽/заказ. 1 заказ = 2–3 недели → рост числа заказов только через делегатов (параллельные потоки). В плане 6 заказов/мес по текущей мощности.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>• Почасовая: 2 500 ₽/ч, рост до 60 ч/мес (~14 ч/нед).</t>
-        </is>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>До цели (цель − доход факт)</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>B4-C12</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>• RealMind/Академия: цена проекта 50 000 ₽ — ЗАГЛУШКА, задать реальную. Этот канал закрывает разрыв цели (~250 500).</t>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>ПОЯСНЕНИЯ:</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>• «Нужно ед./мес» — сколько продать/отработать, чтобы выйти на плановую сумму.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A17:H17"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>СВОДКА</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Расходы, факт / мес</t>
-        </is>
-      </c>
-      <c r="B3" s="13">
-        <f>Расходы.C19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Доход, факт / мес</t>
-        </is>
-      </c>
-      <c r="B4" s="13">
-        <f>Доходы.F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Профицит сейчас (доход − расход)</t>
-        </is>
-      </c>
-      <c r="B5" s="13">
-        <f>B4-B3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Цель дохода / мес</t>
-        </is>
-      </c>
-      <c r="B6" s="13">
-        <f>Доходы.B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>До цели (цель − факт дохода)</t>
-        </is>
-      </c>
-      <c r="B7" s="13">
-        <f>B6-B4</f>
-        <v/>
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>• «штук в месяц» = цель ÷ стоимость единицы (сколько продать ЭТОГО, чтобы одному каналу закрыть всю цель).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>• Гипнотерапия: $150 × курс. Делегирование: 30% × 87 500 = 26 250 ₽/заказ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>• 1 заказ делегирования = 2–3 недели → рост числа только через делегатов (параллельные потоки).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>• RealMind/Академия: цена проекта 50 000 ₽ — ЗАГЛУШКА, поставь реальную.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>• Долги 22 200 = 266 400 ₽ ÷ 12 мес. Жильё = 0 (допущение).</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
